--- a/data/fmsForecastOutput/File1/RPT_RPT5721799034895YM_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT5721799034895YM_fmsForecastOutput.xlsx
@@ -1884,7 +1884,7 @@
         <v>527.0813055023985</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>559.7245857367685</v>
+        <v>559.7245857367687</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>597.2538105127551</v>
@@ -1899,7 +1899,7 @@
         <v>50.70525129310629</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>57.43209229682002</v>
+        <v>57.43209229682003</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>66.03487987702295</v>
@@ -1914,7 +1914,7 @@
         <v>62454794.63757282</v>
       </c>
       <c r="P8" s="152" t="n">
-        <v>71627802.53844024</v>
+        <v>71627802.53844026</v>
       </c>
       <c r="Q8" s="153" t="n">
         <v>83646847.68341915</v>
@@ -1934,7 +1934,7 @@
         <v>535.9755798469399</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>569.1697016438529</v>
+        <v>569.169701643853</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>607.3322162322669</v>
@@ -1949,7 +1949,7 @@
         <v>61.61293524298219</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>69.69052532211306</v>
+        <v>69.69052532211307</v>
       </c>
       <c r="AC8" s="150" t="n">
         <v>79.99241380256164</v>
@@ -1964,7 +1964,7 @@
         <v>62454794.63757282</v>
       </c>
       <c r="AG8" s="152" t="n">
-        <v>71627802.53844024</v>
+        <v>71627802.53844026</v>
       </c>
       <c r="AH8" s="153" t="n">
         <v>83646847.68341915</v>
@@ -2022,10 +2022,10 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>881.2266846643852</v>
+        <v>881.2266846643851</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>978.3936331962973</v>
+        <v>978.3936331962968</v>
       </c>
       <c r="E9" s="156" t="n">
         <v>1076.830698795232</v>
@@ -2037,34 +2037,34 @@
         <v>1202.071068109859</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>57.6148675797288</v>
+        <v>57.61486757972879</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>65.02641382203009</v>
+        <v>65.02641382203007</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>74.0475409854175</v>
+        <v>74.04754098541748</v>
       </c>
       <c r="K9" s="156" t="n">
         <v>83.07780039800058</v>
       </c>
       <c r="L9" s="157" t="n">
-        <v>94.7945009558062</v>
+        <v>94.79450095580297</v>
       </c>
       <c r="M9" s="158" t="n">
         <v>15281293.46325165</v>
       </c>
       <c r="N9" s="159" t="n">
-        <v>17345717.63787505</v>
+        <v>17345717.63787504</v>
       </c>
       <c r="O9" s="159" t="n">
-        <v>19853448.29827568</v>
+        <v>19853448.29827567</v>
       </c>
       <c r="P9" s="159" t="n">
         <v>22367040.03683541</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>25682956.38414068</v>
+        <v>25682956.38414076</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>895.0820100434429</v>
+        <v>895.0820100434428</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>993.7766922577642</v>
+        <v>993.776692257764</v>
       </c>
       <c r="V9" s="156" t="n">
         <v>1093.761461298921</v>
@@ -2087,34 +2087,34 @@
         <v>1220.970956262652</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>57.85944510810379</v>
+        <v>57.85944510810378</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>65.30330806745712</v>
+        <v>65.3033080674571</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>74.36491852139723</v>
+        <v>74.36491852139721</v>
       </c>
       <c r="AB9" s="156" t="n">
         <v>83.43829065658437</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>95.212424221313</v>
+        <v>95.21242422130977</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>15281293.46325165</v>
       </c>
       <c r="AE9" s="159" t="n">
-        <v>17345717.63787505</v>
+        <v>17345717.63787504</v>
       </c>
       <c r="AF9" s="159" t="n">
-        <v>19853448.29827568</v>
+        <v>19853448.29827567</v>
       </c>
       <c r="AG9" s="159" t="n">
         <v>22367040.03683541</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>25682956.38414068</v>
+        <v>25682956.38414076</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2173,22 +2173,22 @@
         <v>506.4552153988976</v>
       </c>
       <c r="D10" s="162" t="n">
-        <v>552.2923887222968</v>
+        <v>552.2923887222967</v>
       </c>
       <c r="E10" s="162" t="n">
         <v>601.102965373508</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>636.5650044966173</v>
+        <v>636.5650044966175</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>677.3085466404946</v>
+        <v>677.3085466404947</v>
       </c>
       <c r="H10" s="161" t="n">
-        <v>41.76444149846836</v>
+        <v>41.76444149846835</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>47.89524604244684</v>
+        <v>47.89524604244683</v>
       </c>
       <c r="J10" s="162" t="n">
         <v>54.87801535325548</v>
@@ -2197,22 +2197,22 @@
         <v>61.98536156944807</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>71.10234016957331</v>
+        <v>71.10234016957288</v>
       </c>
       <c r="M10" s="164" t="n">
-        <v>61049553.31272817</v>
+        <v>61049553.31272816</v>
       </c>
       <c r="N10" s="165" t="n">
-        <v>70971545.47112544</v>
+        <v>70971545.47112542</v>
       </c>
       <c r="O10" s="165" t="n">
         <v>82308242.93584849</v>
       </c>
       <c r="P10" s="165" t="n">
-        <v>93994842.57527566</v>
+        <v>93994842.57527567</v>
       </c>
       <c r="Q10" s="166" t="n">
-        <v>109329804.0675598</v>
+        <v>109329804.0675599</v>
       </c>
       <c r="S10" s="42" t="inlineStr">
         <is>
@@ -2220,49 +2220,49 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>514.91743441011</v>
+        <v>514.9174344101099</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>561.5242405519012</v>
+        <v>561.5242405519011</v>
       </c>
       <c r="V10" s="162" t="n">
         <v>611.153009623626</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>647.2089050293808</v>
+        <v>647.208905029381</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>688.6344813880746</v>
+        <v>688.6344813880748</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>48.96904586106647</v>
+        <v>48.96904586106646</v>
       </c>
       <c r="Z10" s="162" t="n">
-        <v>56.12694363513135</v>
+        <v>56.12694363513133</v>
       </c>
       <c r="AA10" s="162" t="n">
         <v>64.27133039560621</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>72.53443251653451</v>
+        <v>72.53443251653452</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>83.11345205833463</v>
+        <v>83.11345205833408</v>
       </c>
       <c r="AD10" s="164" t="n">
-        <v>61049553.31272817</v>
+        <v>61049553.31272816</v>
       </c>
       <c r="AE10" s="165" t="n">
-        <v>70971545.47112544</v>
+        <v>70971545.47112542</v>
       </c>
       <c r="AF10" s="165" t="n">
         <v>82308242.93584849</v>
       </c>
       <c r="AG10" s="165" t="n">
-        <v>93994842.57527566</v>
+        <v>93994842.57527567</v>
       </c>
       <c r="AH10" s="166" t="n">
-        <v>109329804.0675598</v>
+        <v>109329804.0675599</v>
       </c>
       <c r="AJ10" s="39" t="n"/>
       <c r="AQ10" s="40" t="inlineStr">
@@ -2324,7 +2324,7 @@
         <v>974.3311947755478</v>
       </c>
       <c r="E11" s="156" t="n">
-        <v>1061.699815021288</v>
+        <v>1061.699815021289</v>
       </c>
       <c r="F11" s="156" t="n">
         <v>1133.431450800131</v>
@@ -2339,10 +2339,10 @@
         <v>101.1247656025734</v>
       </c>
       <c r="J11" s="156" t="n">
-        <v>114.4891849590058</v>
+        <v>114.4891849590059</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>128.8574239897535</v>
+        <v>128.8574239897536</v>
       </c>
       <c r="L11" s="157" t="n">
         <v>146.8939287861138</v>
@@ -2354,10 +2354,10 @@
         <v>6428189.345706714</v>
       </c>
       <c r="O11" s="159" t="n">
-        <v>7361192.68722243</v>
+        <v>7361192.687222432</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>8374037.947878093</v>
+        <v>8374037.947878095</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>9674380.582872599</v>
@@ -2374,7 +2374,7 @@
         <v>1237.349223785199</v>
       </c>
       <c r="V11" s="156" t="n">
-        <v>1348.302763016953</v>
+        <v>1348.302763016954</v>
       </c>
       <c r="W11" s="156" t="n">
         <v>1439.398156788308</v>
@@ -2392,7 +2392,7 @@
         <v>131.1819336447159</v>
       </c>
       <c r="AB11" s="156" t="n">
-        <v>147.7398256443604</v>
+        <v>147.7398256443605</v>
       </c>
       <c r="AC11" s="157" t="n">
         <v>168.5446406658589</v>
@@ -2404,10 +2404,10 @@
         <v>6428189.345706714</v>
       </c>
       <c r="AF11" s="159" t="n">
-        <v>7361192.68722243</v>
+        <v>7361192.687222432</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>8374037.947878093</v>
+        <v>8374037.947878095</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>9674380.582872599</v>
@@ -2464,37 +2464,37 @@
         <v>525.5424121208454</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>572.9022709483426</v>
+        <v>572.9022709483423</v>
       </c>
       <c r="E12" s="162" t="n">
         <v>623.3013323322406</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>660.2413178815325</v>
+        <v>660.2413178815327</v>
       </c>
       <c r="G12" s="163" t="n">
-        <v>702.7031942079863</v>
+        <v>702.7031942079864</v>
       </c>
       <c r="H12" s="161" t="n">
         <v>43.72142799530198</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>50.08477099359556</v>
+        <v>50.08477099359555</v>
       </c>
       <c r="J12" s="162" t="n">
-        <v>57.32841466128746</v>
+        <v>57.32841466128745</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>64.73345193624057</v>
+        <v>64.73345193624058</v>
       </c>
       <c r="L12" s="163" t="n">
-        <v>74.215285256737</v>
+        <v>74.21528525673658</v>
       </c>
       <c r="M12" s="164" t="n">
         <v>66655485.80932541</v>
       </c>
       <c r="N12" s="165" t="n">
-        <v>77399734.81683214</v>
+        <v>77399734.81683213</v>
       </c>
       <c r="O12" s="165" t="n">
         <v>89669435.62307094</v>
@@ -2503,7 +2503,7 @@
         <v>102368880.5231538</v>
       </c>
       <c r="Q12" s="166" t="n">
-        <v>119004184.6504324</v>
+        <v>119004184.6504325</v>
       </c>
       <c r="S12" s="42" t="inlineStr">
         <is>
@@ -2514,37 +2514,37 @@
         <v>539.6595269768121</v>
       </c>
       <c r="U12" s="162" t="n">
-        <v>588.2063942372233</v>
+        <v>588.2063942372232</v>
       </c>
       <c r="V12" s="162" t="n">
         <v>639.8717222332704</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>677.7205504694526</v>
+        <v>677.7205504694527</v>
       </c>
       <c r="X12" s="163" t="n">
-        <v>721.1908606362679</v>
+        <v>721.190860636268</v>
       </c>
       <c r="Y12" s="161" t="n">
         <v>51.21265005541488</v>
       </c>
       <c r="Z12" s="162" t="n">
-        <v>58.6368143311067</v>
+        <v>58.63681433110669</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>67.0801151981707</v>
+        <v>67.08011519817072</v>
       </c>
       <c r="AB12" s="162" t="n">
         <v>75.6860554032601</v>
       </c>
       <c r="AC12" s="163" t="n">
-        <v>86.68542807725234</v>
+        <v>86.68542807725174</v>
       </c>
       <c r="AD12" s="164" t="n">
         <v>66655485.80932541</v>
       </c>
       <c r="AE12" s="165" t="n">
-        <v>77399734.81683214</v>
+        <v>77399734.81683213</v>
       </c>
       <c r="AF12" s="165" t="n">
         <v>89669435.62307094</v>
@@ -2553,7 +2553,7 @@
         <v>102368880.5231538</v>
       </c>
       <c r="AH12" s="166" t="n">
-        <v>119004184.6504324</v>
+        <v>119004184.6504325</v>
       </c>
       <c r="AQ12" s="40" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>3469.630894069584</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>3695.3851405864</v>
+        <v>3695.385140586401</v>
       </c>
       <c r="H13" s="155" t="n">
         <v>2655.868210096912</v>
@@ -2630,10 +2630,10 @@
         <v>3074.967999833879</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>3292.912981338575</v>
+        <v>3292.912981338576</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>65207274.24222936</v>
+        <v>65207274.24222937</v>
       </c>
       <c r="N13" s="159" t="n">
         <v>74794356.03350759</v>
@@ -2683,7 +2683,7 @@
         <v>2388.566174501259</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>65207274.24222936</v>
+        <v>65207274.24222937</v>
       </c>
       <c r="AE13" s="159" t="n">
         <v>74794356.03350759</v>
@@ -2749,13 +2749,13 @@
         <v>887.2141616043457</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>956.3842863523615</v>
+        <v>956.3842863523612</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>1042.355791489744</v>
+        <v>1042.355791489745</v>
       </c>
       <c r="F14" s="168" t="n">
-        <v>1109.580926965818</v>
+        <v>1109.580926965817</v>
       </c>
       <c r="G14" s="169" t="n">
         <v>1191.670822238224</v>
@@ -2764,7 +2764,7 @@
         <v>85.12207773520258</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>96.78590093043991</v>
+        <v>96.78590093043989</v>
       </c>
       <c r="J14" s="168" t="n">
         <v>111.4671416337965</v>
@@ -2773,7 +2773,7 @@
         <v>126.8303638726825</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>147.033217406226</v>
+        <v>147.0332174062251</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>131862760.0515548</v>
@@ -2788,7 +2788,7 @@
         <v>204792952.1891128</v>
       </c>
       <c r="Q14" s="172" t="n">
-        <v>241225048.3266106</v>
+        <v>241225048.3266107</v>
       </c>
       <c r="S14" s="51" t="inlineStr">
         <is>
@@ -2799,7 +2799,7 @@
         <v>859.5093508742751</v>
       </c>
       <c r="U14" s="168" t="n">
-        <v>924.845311304806</v>
+        <v>924.8453113048058</v>
       </c>
       <c r="V14" s="168" t="n">
         <v>1005.915160794637</v>
@@ -2814,7 +2814,7 @@
         <v>98.74428156369022</v>
       </c>
       <c r="Z14" s="168" t="n">
-        <v>112.1248011616786</v>
+        <v>112.1248011616785</v>
       </c>
       <c r="AA14" s="168" t="n">
         <v>128.939093192049</v>
@@ -2823,7 +2823,7 @@
         <v>146.4400814694964</v>
       </c>
       <c r="AC14" s="169" t="n">
-        <v>169.3999510170991</v>
+        <v>169.3999510170979</v>
       </c>
       <c r="AD14" s="170" t="n">
         <v>131862760.0515548</v>
@@ -2838,7 +2838,7 @@
         <v>204792952.1891128</v>
       </c>
       <c r="AH14" s="172" t="n">
-        <v>241225048.3266106</v>
+        <v>241225048.3266107</v>
       </c>
       <c r="AR14" s="58" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>19689.72928516593</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>21365.5889951038</v>
+        <v>21365.58899510386</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>247890.8390778529</v>
@@ -3316,7 +3316,7 @@
         <v>249540.3168845894</v>
       </c>
       <c r="L20" s="81" t="n">
-        <v>249567.388394737</v>
+        <v>249567.388394747</v>
       </c>
       <c r="M20" s="79" t="n">
         <v>265231.7727209047</v>
@@ -3331,7 +3331,7 @@
         <v>269230.0461697553</v>
       </c>
       <c r="Q20" s="81" t="n">
-        <v>270932.9773898408</v>
+        <v>270932.9773898508</v>
       </c>
       <c r="S20" s="32" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>19384.9442455713</v>
       </c>
       <c r="X20" s="81" t="n">
-        <v>21034.86266598452</v>
+        <v>21034.86266598458</v>
       </c>
       <c r="Y20" s="79" t="n">
         <v>247038.1055676015</v>
@@ -3366,7 +3366,7 @@
         <v>248681.9092437189</v>
       </c>
       <c r="AC20" s="81" t="n">
-        <v>248708.8876290703</v>
+        <v>248708.8876290802</v>
       </c>
       <c r="AD20" s="79" t="n">
         <v>264110.6120997236</v>
@@ -3381,7 +3381,7 @@
         <v>268066.8534892902</v>
       </c>
       <c r="AH20" s="81" t="n">
-        <v>269743.7502950548</v>
+        <v>269743.7502950648</v>
       </c>
       <c r="AS20" s="82" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>1368744.420106977</v>
       </c>
       <c r="L21" s="87" t="n">
-        <v>1376222.004999609</v>
+        <v>1376222.004999619</v>
       </c>
       <c r="M21" s="85" t="n">
         <v>1461759.121451847</v>
@@ -3451,7 +3451,7 @@
         <v>1516403.876582447</v>
       </c>
       <c r="Q21" s="87" t="n">
-        <v>1537640.024320116</v>
+        <v>1537640.024320126</v>
       </c>
       <c r="S21" s="42" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
         <v>145231.0712118658</v>
       </c>
       <c r="X21" s="87" t="n">
-        <v>158763.1857283485</v>
+        <v>158763.1857283486</v>
       </c>
       <c r="Y21" s="85" t="n">
         <v>1128134.981019596</v>
@@ -3486,7 +3486,7 @@
         <v>1150634.069166108</v>
       </c>
       <c r="AC21" s="87" t="n">
-        <v>1156665.320247132</v>
+        <v>1156665.320247141</v>
       </c>
       <c r="AD21" s="85" t="n">
         <v>1246696.811000487</v>
@@ -3501,7 +3501,7 @@
         <v>1295865.140377974</v>
       </c>
       <c r="AH21" s="87" t="n">
-        <v>1315428.50597548</v>
+        <v>1315428.50597549</v>
       </c>
       <c r="AR21" s="20" t="inlineStr">
         <is>
@@ -3706,16 +3706,16 @@
         <v>126831.7918250114</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>135101.1136484238</v>
+        <v>135101.1136484239</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>143862.0952205411</v>
       </c>
       <c r="F23" s="86" t="n">
-        <v>155047.6738590327</v>
+        <v>155047.6738590326</v>
       </c>
       <c r="G23" s="87" t="n">
-        <v>169351.990472395</v>
+        <v>169351.9904723951</v>
       </c>
       <c r="H23" s="85" t="n">
         <v>1397717.813839464</v>
@@ -3730,7 +3730,7 @@
         <v>1426343.05166542</v>
       </c>
       <c r="L23" s="87" t="n">
-        <v>1434147.669183358</v>
+        <v>1434147.669183368</v>
       </c>
       <c r="M23" s="85" t="n">
         <v>1524549.605664476</v>
@@ -3745,7 +3745,7 @@
         <v>1581390.725524453</v>
       </c>
       <c r="Q23" s="87" t="n">
-        <v>1603499.659655753</v>
+        <v>1603499.659655763</v>
       </c>
       <c r="S23" s="42" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>151048.8068455996</v>
       </c>
       <c r="X23" s="87" t="n">
-        <v>165010.6665875403</v>
+        <v>165010.6665875404</v>
       </c>
       <c r="Y23" s="85" t="n">
         <v>1178029.421998275</v>
@@ -3777,10 +3777,10 @@
         <v>1196614.784709081</v>
       </c>
       <c r="AB23" s="86" t="n">
-        <v>1201497.312485443</v>
+        <v>1201497.312485444</v>
       </c>
       <c r="AC23" s="87" t="n">
-        <v>1207817.354107913</v>
+        <v>1207817.354107923</v>
       </c>
       <c r="AD23" s="85" t="n">
         <v>1301543.38307431</v>
@@ -3795,7 +3795,7 @@
         <v>1352546.119331043</v>
       </c>
       <c r="AH23" s="87" t="n">
-        <v>1372828.020695454</v>
+        <v>1372828.020695464</v>
       </c>
       <c r="AR23" s="90" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>1430131.875877583</v>
       </c>
       <c r="L25" s="93" t="n">
-        <v>1438190.087282662</v>
+        <v>1438190.087282672</v>
       </c>
       <c r="M25" s="91" t="n">
         <v>1549101.755501704</v>
@@ -3984,7 +3984,7 @@
         <v>1614699.713348551</v>
       </c>
       <c r="Q25" s="93" t="n">
-        <v>1640615.995364842</v>
+        <v>1640615.995364852</v>
       </c>
       <c r="S25" s="51" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         <v>1206923.968031044</v>
       </c>
       <c r="AC25" s="93" t="n">
-        <v>1213607.226999297</v>
+        <v>1213607.226999307</v>
       </c>
       <c r="AD25" s="91" t="n">
         <v>1335396.419553705</v>
@@ -4034,7 +4034,7 @@
         <v>1398476.087516869</v>
       </c>
       <c r="AH25" s="93" t="n">
-        <v>1423997.155124689</v>
+        <v>1423997.155124698</v>
       </c>
     </row>
     <row r="28" ht="1.95" customHeight="1">
@@ -4417,7 +4417,7 @@
         <v>558.1979235466482</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>600.2901078628598</v>
+        <v>600.2901078628601</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>642.1502042819844</v>
@@ -4432,7 +4432,7 @@
         <v>53.69867170254653</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>61.59443011470897</v>
+        <v>61.59443011470898</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>70.9988129943643</v>
@@ -4447,7 +4447,7 @@
         <v>66141857.65703816</v>
       </c>
       <c r="P35" s="152" t="n">
-        <v>76818961.33824842</v>
+        <v>76818961.33824843</v>
       </c>
       <c r="Q35" s="153" t="n">
         <v>89934696.74364601</v>
@@ -4467,7 +4467,7 @@
         <v>567.6172776742717</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>610.4197498173539</v>
+        <v>610.419749817354</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>652.9862176781401</v>
@@ -4482,7 +4482,7 @@
         <v>65.25029849705086</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>74.74128174584935</v>
+        <v>74.74128174584936</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>86.00555402103539</v>
@@ -4497,7 +4497,7 @@
         <v>66141857.65703816</v>
       </c>
       <c r="AG35" s="152" t="n">
-        <v>76818961.33824842</v>
+        <v>76818961.33824843</v>
       </c>
       <c r="AH35" s="153" t="n">
         <v>89934696.74364601</v>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>906.3644627480769</v>
+        <v>906.3644627480768</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>1029.978957210314</v>
+        <v>1029.978957210313</v>
       </c>
       <c r="E36" s="156" t="n">
         <v>1140.856746064072</v>
@@ -4525,25 +4525,25 @@
         <v>1292.9663330623</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>59.25838312543892</v>
+        <v>59.25838312543891</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>68.45489956914241</v>
+        <v>68.45489956914238</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>78.45024919626061</v>
+        <v>78.4502491962606</v>
       </c>
       <c r="K36" s="156" t="n">
         <v>89.13436723154597</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>101.9624392824151</v>
+        <v>101.9624392824117</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>15717206.00493471</v>
       </c>
       <c r="N36" s="159" t="n">
-        <v>18260262.08526916</v>
+        <v>18260262.08526915</v>
       </c>
       <c r="O36" s="159" t="n">
         <v>21033891.81703589</v>
@@ -4552,7 +4552,7 @@
         <v>23997649.80506105</v>
       </c>
       <c r="Q36" s="160" t="n">
-        <v>27624987.25671559</v>
+        <v>27624987.25671567</v>
       </c>
       <c r="S36" s="32" t="inlineStr">
         <is>
@@ -4560,13 +4560,13 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>920.615023655878</v>
+        <v>920.6150236558778</v>
       </c>
       <c r="U36" s="156" t="n">
         <v>1046.173080509208</v>
       </c>
       <c r="V36" s="156" t="n">
-        <v>1158.794175448239</v>
+        <v>1158.794175448238</v>
       </c>
       <c r="W36" s="156" t="n">
         <v>1237.95299594651</v>
@@ -4575,25 +4575,25 @@
         <v>1313.295346652677</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>59.50993744620972</v>
+        <v>59.50993744620971</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>68.74639292773141</v>
+        <v>68.74639292773138</v>
       </c>
       <c r="AA36" s="156" t="n">
-        <v>78.78649732085138</v>
+        <v>78.78649732085137</v>
       </c>
       <c r="AB36" s="156" t="n">
         <v>89.52113807692305</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>102.4119640455004</v>
+        <v>102.4119640454969</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>15717206.00493471</v>
       </c>
       <c r="AE36" s="159" t="n">
-        <v>18260262.08526916</v>
+        <v>18260262.08526915</v>
       </c>
       <c r="AF36" s="159" t="n">
         <v>21033891.81703589</v>
@@ -4602,7 +4602,7 @@
         <v>23997649.80506105</v>
       </c>
       <c r="AH36" s="160" t="n">
-        <v>27624987.25671559</v>
+        <v>27624987.25671567</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" thickTop="1">
@@ -4612,40 +4612,40 @@
         </is>
       </c>
       <c r="C37" s="161" t="n">
-        <v>520.7513229582903</v>
+        <v>520.7513229582902</v>
       </c>
       <c r="D37" s="162" t="n">
-        <v>581.2414160333865</v>
+        <v>581.2414160333864</v>
       </c>
       <c r="E37" s="162" t="n">
         <v>636.6507125946796</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>682.764338632505</v>
+        <v>682.7643386325051</v>
       </c>
       <c r="G37" s="163" t="n">
-        <v>728.2934364777361</v>
+        <v>728.2934364777362</v>
       </c>
       <c r="H37" s="161" t="n">
-        <v>42.94335906050748</v>
+        <v>42.94335906050747</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>50.40572928296697</v>
+        <v>50.40572928296696</v>
       </c>
       <c r="J37" s="162" t="n">
         <v>58.12336586748051</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>66.48401042769827</v>
+        <v>66.48401042769828</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>76.45462015879946</v>
+        <v>76.45462015879902</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>62772846.81247862</v>
       </c>
       <c r="N37" s="165" t="n">
-        <v>74691598.92488927</v>
+        <v>74691598.92488925</v>
       </c>
       <c r="O37" s="165" t="n">
         <v>87175749.47407405</v>
@@ -4654,7 +4654,7 @@
         <v>100816611.1433095</v>
       </c>
       <c r="Q37" s="166" t="n">
-        <v>117559684.0003616</v>
+        <v>117559684.0003617</v>
       </c>
       <c r="S37" s="42" t="inlineStr">
         <is>
@@ -4662,40 +4662,40 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>529.4524116454327</v>
+        <v>529.4524116454326</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>590.957165769615</v>
+        <v>590.9571657696149</v>
       </c>
       <c r="V37" s="162" t="n">
         <v>647.2950916811642</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>694.1807307627466</v>
+        <v>694.1807307627467</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>740.4719391402987</v>
+        <v>740.4719391402989</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>50.35133342653117</v>
+        <v>50.35133342653116</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>59.06890057200017</v>
+        <v>59.06890057200016</v>
       </c>
       <c r="AA37" s="162" t="n">
         <v>68.07217840016025</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>77.79869062138948</v>
+        <v>77.7986906213895</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>89.36987716651545</v>
+        <v>89.36987716651485</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>62772846.81247862</v>
       </c>
       <c r="AE37" s="165" t="n">
-        <v>74691598.92488927</v>
+        <v>74691598.92488925</v>
       </c>
       <c r="AF37" s="165" t="n">
         <v>87175749.47407405</v>
@@ -4704,7 +4704,7 @@
         <v>100816611.1433095</v>
       </c>
       <c r="AH37" s="166" t="n">
-        <v>117559684.0003616</v>
+        <v>117559684.0003617</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" thickBot="1">
@@ -4750,10 +4750,10 @@
         <v>6765779.976775518</v>
       </c>
       <c r="O38" s="159" t="n">
-        <v>7797347.659210338</v>
+        <v>7797347.65921034</v>
       </c>
       <c r="P38" s="159" t="n">
-        <v>8982776.760550831</v>
+        <v>8982776.760550832</v>
       </c>
       <c r="Q38" s="160" t="n">
         <v>10403905.47481582</v>
@@ -4773,7 +4773,7 @@
         <v>1428.190490294579</v>
       </c>
       <c r="W38" s="156" t="n">
-        <v>1544.03316446088</v>
+        <v>1544.033164460881</v>
       </c>
       <c r="X38" s="157" t="n">
         <v>1665.296094426409</v>
@@ -4788,7 +4788,7 @@
         <v>138.9545399362813</v>
       </c>
       <c r="AB38" s="156" t="n">
-        <v>158.4795627469387</v>
+        <v>158.4795627469388</v>
       </c>
       <c r="AC38" s="157" t="n">
         <v>181.25424100834</v>
@@ -4800,10 +4800,10 @@
         <v>6765779.976775518</v>
       </c>
       <c r="AF38" s="159" t="n">
-        <v>7797347.659210338</v>
+        <v>7797347.65921034</v>
       </c>
       <c r="AG38" s="159" t="n">
-        <v>8982776.760550831</v>
+        <v>8982776.760550832</v>
       </c>
       <c r="AH38" s="160" t="n">
         <v>10403905.47481582</v>
@@ -4819,22 +4819,22 @@
         <v>540.3812570189348</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>602.9363985380819</v>
+        <v>602.9363985380817</v>
       </c>
       <c r="E39" s="162" t="n">
         <v>660.1676208572542</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>708.1653350290728</v>
+        <v>708.165335029073</v>
       </c>
       <c r="G39" s="163" t="n">
-        <v>755.6072362552831</v>
+        <v>755.6072362552832</v>
       </c>
       <c r="H39" s="161" t="n">
         <v>44.95591540066118</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>52.71044116214716</v>
+        <v>52.71044116214715</v>
       </c>
       <c r="J39" s="162" t="n">
         <v>60.71920779127564</v>
@@ -4843,13 +4843,13 @@
         <v>69.43216886987017</v>
       </c>
       <c r="L39" s="163" t="n">
-        <v>79.80269200845933</v>
+        <v>79.80269200845886</v>
       </c>
       <c r="M39" s="164" t="n">
         <v>68537523.09636353</v>
       </c>
       <c r="N39" s="165" t="n">
-        <v>81457378.90166478</v>
+        <v>81457378.90166476</v>
       </c>
       <c r="O39" s="165" t="n">
         <v>94973097.13328439</v>
@@ -4858,7 +4858,7 @@
         <v>109799387.9038603</v>
       </c>
       <c r="Q39" s="166" t="n">
-        <v>127963589.4751774</v>
+        <v>127963589.4751775</v>
       </c>
       <c r="S39" s="42" t="inlineStr">
         <is>
@@ -4869,37 +4869,37 @@
         <v>554.8969727735632</v>
       </c>
       <c r="U39" s="162" t="n">
-        <v>619.042833171874</v>
+        <v>619.0428331718739</v>
       </c>
       <c r="V39" s="162" t="n">
         <v>677.7180965424384</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>726.9133083328227</v>
+        <v>726.9133083328228</v>
       </c>
       <c r="X39" s="163" t="n">
-        <v>775.4867738037474</v>
+        <v>775.4867738037475</v>
       </c>
       <c r="Y39" s="161" t="n">
         <v>52.6586543235113</v>
       </c>
       <c r="Z39" s="162" t="n">
-        <v>61.71082128199747</v>
+        <v>61.71082128199746</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>71.04769035469022</v>
+        <v>71.04769035469023</v>
       </c>
       <c r="AB39" s="162" t="n">
         <v>81.17977371312563</v>
       </c>
       <c r="AC39" s="163" t="n">
-        <v>93.2116678463141</v>
+        <v>93.21166784631346</v>
       </c>
       <c r="AD39" s="164" t="n">
         <v>68537523.09636353</v>
       </c>
       <c r="AE39" s="165" t="n">
-        <v>81457378.90166478</v>
+        <v>81457378.90166476</v>
       </c>
       <c r="AF39" s="165" t="n">
         <v>94973097.13328439</v>
@@ -4908,7 +4908,7 @@
         <v>109799387.9038603</v>
       </c>
       <c r="AH39" s="166" t="n">
-        <v>127963589.4751774</v>
+        <v>127963589.4751775</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" thickBot="1">
@@ -4918,7 +4918,7 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>3077.561852826308</v>
+        <v>3077.561852826309</v>
       </c>
       <c r="D40" s="156" t="n">
         <v>3276.191295399594</v>
@@ -4930,7 +4930,7 @@
         <v>3722.77992925921</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>3974.81460749317</v>
+        <v>3974.814607493171</v>
       </c>
       <c r="H40" s="155" t="n">
         <v>2731.81260038769</v>
@@ -4945,10 +4945,10 @@
         <v>3299.321888233776</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>3541.909197954797</v>
+        <v>3541.909197954798</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>67071872.29194545</v>
+        <v>67071872.29194546</v>
       </c>
       <c r="N40" s="159" t="n">
         <v>78739189.42363153</v>
@@ -4960,7 +4960,7 @@
         <v>109897072.6029604</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>131462690.8423988</v>
+        <v>131462690.8423989</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         <v>2569.179492848509</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>67071872.29194545</v>
+        <v>67071872.29194546</v>
       </c>
       <c r="AE40" s="159" t="n">
         <v>78739189.42363153</v>
@@ -5010,7 +5010,7 @@
         <v>109897072.6029604</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>131462690.8423988</v>
+        <v>131462690.8423989</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,22 +5020,22 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>912.4227036357422</v>
+        <v>912.4227036357424</v>
       </c>
       <c r="D41" s="180" t="n">
         <v>1006.671677053116</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1104.214203457709</v>
+        <v>1104.21420345771</v>
       </c>
       <c r="F41" s="180" t="n">
-        <v>1190.329060128792</v>
+        <v>1190.329060128791</v>
       </c>
       <c r="G41" s="181" t="n">
         <v>1281.586348187484</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>87.5406634242626</v>
+        <v>87.54066342426262</v>
       </c>
       <c r="I41" s="180" t="n">
         <v>101.8749749395672</v>
@@ -5047,7 +5047,7 @@
         <v>136.0602585673444</v>
       </c>
       <c r="L41" s="181" t="n">
-        <v>158.1273625580401</v>
+        <v>158.1273625580393</v>
       </c>
       <c r="M41" s="182" t="n">
         <v>135609395.388309</v>
@@ -5062,7 +5062,7 @@
         <v>219696460.5068207</v>
       </c>
       <c r="Q41" s="184" t="n">
-        <v>259426280.3175763</v>
+        <v>259426280.3175764</v>
       </c>
       <c r="S41" s="51" t="inlineStr">
         <is>
@@ -5070,19 +5070,19 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>883.9307121820254</v>
+        <v>883.9307121820257</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>973.474359451056</v>
       </c>
       <c r="V41" s="186" t="n">
-        <v>1065.611010263007</v>
+        <v>1065.611010263008</v>
       </c>
       <c r="W41" s="186" t="n">
         <v>1146.927849697214</v>
       </c>
       <c r="X41" s="187" t="n">
-        <v>1233.073667685076</v>
+        <v>1233.073667685077</v>
       </c>
       <c r="Y41" s="185" t="n">
         <v>101.5499168656078</v>
@@ -5097,7 +5097,7 @@
         <v>157.0970447531307</v>
       </c>
       <c r="AC41" s="187" t="n">
-        <v>182.1817405912306</v>
+        <v>182.1817405912294</v>
       </c>
       <c r="AD41" s="188" t="n">
         <v>135609395.388309</v>
@@ -5112,7 +5112,7 @@
         <v>219696460.5068207</v>
       </c>
       <c r="AH41" s="190" t="n">
-        <v>259426280.3175763</v>
+        <v>259426280.3175764</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" thickBot="1"/>
@@ -5500,7 +5500,7 @@
         <v>0.003010854622556073</v>
       </c>
       <c r="L47" s="157" t="n">
-        <v>0.003133426913346806</v>
+        <v>0.003133426913346699</v>
       </c>
       <c r="M47" s="158" t="n">
         <v>699.2922532076233</v>
@@ -5515,7 +5515,7 @@
         <v>810.6125290411929</v>
       </c>
       <c r="Q47" s="160" t="n">
-        <v>848.9486830665088</v>
+        <v>848.9486830665112</v>
       </c>
       <c r="S47" s="32" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>0.003023919289124564</v>
       </c>
       <c r="AC47" s="157" t="n">
-        <v>0.003147241343452444</v>
+        <v>0.003147241343452336</v>
       </c>
       <c r="AD47" s="158" t="n">
         <v>699.2922532076233</v>
@@ -5565,7 +5565,7 @@
         <v>810.6125290411929</v>
       </c>
       <c r="AH47" s="160" t="n">
-        <v>848.9486830665088</v>
+        <v>848.9486830665112</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" thickTop="1">
@@ -5587,7 +5587,7 @@
         <v>0.2214318850621837</v>
       </c>
       <c r="G48" s="163" t="n">
-        <v>0.2419494859018763</v>
+        <v>0.2419494859018762</v>
       </c>
       <c r="H48" s="161" t="n">
         <v>0.01330637982857661</v>
@@ -5602,7 +5602,7 @@
         <v>0.02156187563191255</v>
       </c>
       <c r="L48" s="163" t="n">
-        <v>0.02539931724732802</v>
+        <v>0.02539931724732785</v>
       </c>
       <c r="M48" s="164" t="n">
         <v>19450.72208792473</v>
@@ -5637,7 +5637,7 @@
         <v>0.2251344118155165</v>
       </c>
       <c r="X48" s="163" t="n">
-        <v>0.2459953585003062</v>
+        <v>0.2459953585003061</v>
       </c>
       <c r="Y48" s="161" t="n">
         <v>0.01560180624214104</v>
@@ -5652,7 +5652,7 @@
         <v>0.02523141550445903</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.02968995016641655</v>
+        <v>0.02968995016641633</v>
       </c>
       <c r="AD48" s="164" t="n">
         <v>19450.72208792473</v>
@@ -5689,7 +5689,7 @@
         <v>0.24735790654064</v>
       </c>
       <c r="G49" s="157" t="n">
-        <v>0.2573797525925845</v>
+        <v>0.2573797525925846</v>
       </c>
       <c r="H49" s="155" t="n">
         <v>0.02155430161736038</v>
@@ -5739,7 +5739,7 @@
         <v>0.3141314937840004</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.3268587096421818</v>
+        <v>0.3268587096421819</v>
       </c>
       <c r="Y49" s="155" t="n">
         <v>0.02467620097747285</v>
@@ -5748,13 +5748,13 @@
         <v>0.02678838028969381</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.02930296653847631</v>
+        <v>0.0293029665384763</v>
       </c>
       <c r="AB49" s="156" t="n">
         <v>0.03224245626700228</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.03557597206373388</v>
+        <v>0.03557597206373389</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1353.405035419108</v>
@@ -5782,16 +5782,16 @@
         <v>0.164029277076264</v>
       </c>
       <c r="D50" s="162" t="n">
-        <v>0.1817355244422655</v>
+        <v>0.1817355244422654</v>
       </c>
       <c r="E50" s="162" t="n">
         <v>0.2022041730736412</v>
       </c>
       <c r="F50" s="162" t="n">
-        <v>0.2226672927133032</v>
+        <v>0.2226672927133033</v>
       </c>
       <c r="G50" s="163" t="n">
-        <v>0.2426723784433133</v>
+        <v>0.2426723784433132</v>
       </c>
       <c r="H50" s="161" t="n">
         <v>0.01364608081366847</v>
@@ -5806,7 +5806,7 @@
         <v>0.02183144571575531</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.02562959715929615</v>
+        <v>0.02562959715929599</v>
       </c>
       <c r="M50" s="164" t="n">
         <v>20804.12712334383</v>
@@ -5841,7 +5841,7 @@
         <v>0.2285621879488006</v>
       </c>
       <c r="X50" s="163" t="n">
-        <v>0.2490569317241254</v>
+        <v>0.2490569317241253</v>
       </c>
       <c r="Y50" s="161" t="n">
         <v>0.01598419798670364</v>
@@ -5853,10 +5853,10 @@
         <v>0.02176135124335126</v>
       </c>
       <c r="AB50" s="162" t="n">
-        <v>0.02552522630190332</v>
+        <v>0.02552522630190331</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.02993605149552987</v>
+        <v>0.02993605149552965</v>
       </c>
       <c r="AD50" s="164" t="n">
         <v>20804.12712334383</v>
@@ -5992,7 +5992,7 @@
         <v>0.1706388702344649</v>
       </c>
       <c r="F52" s="180" t="n">
-        <v>0.1870534230272735</v>
+        <v>0.1870534230272734</v>
       </c>
       <c r="G52" s="181" t="n">
         <v>0.2030226798111289</v>
@@ -6010,7 +6010,7 @@
         <v>0.02138109364501609</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.02504976815912747</v>
+        <v>0.02504976815912732</v>
       </c>
       <c r="M52" s="182" t="n">
         <v>20804.12712334383</v>
@@ -6060,7 +6060,7 @@
         <v>0.0246869046155711</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.02886034580486706</v>
+        <v>0.02886034580486687</v>
       </c>
       <c r="AD52" s="188" t="n">
         <v>20804.12712334383</v>
@@ -6343,7 +6343,7 @@
         <v>0.008856602732167729</v>
       </c>
       <c r="F57" s="149" t="n">
-        <v>0.0003219019782294297</v>
+        <v>0.0003219019782294295</v>
       </c>
       <c r="G57" s="150" t="n">
         <v>0</v>
@@ -6358,7 +6358,7 @@
         <v>0.000852005681950207</v>
       </c>
       <c r="K57" s="149" t="n">
-        <v>3.302964457040306e-05</v>
+        <v>3.302964457040304e-05</v>
       </c>
       <c r="L57" s="150" t="n">
         <v>0</v>
@@ -6373,7 +6373,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="P57" s="152" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="Q57" s="153" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0.009006054161459894</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003273339381121543</v>
+        <v>0.0003273339381121541</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0.001035288645059688</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>4.007956508736704e-05</v>
+        <v>4.007956508736701e-05</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6423,7 +6423,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="AG57" s="152" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="AH57" s="153" t="n">
         <v>0</v>
@@ -6547,7 +6547,7 @@
         <v>0.007664094940340383</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002789777865861416</v>
+        <v>0.0002789777865861414</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
@@ -6562,7 +6562,7 @@
         <v>0.0006996976292463714</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>2.716539371349968e-05</v>
+        <v>2.716539371349966e-05</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
@@ -6577,7 +6577,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="P59" s="165" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="Q59" s="166" t="n">
         <v>0</v>
@@ -6597,7 +6597,7 @@
         <v>0.007792233541752314</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002836425290559567</v>
+        <v>0.0002836425290559565</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>0.0008194628981539538</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>3.178857664465307e-05</v>
+        <v>3.178857664465305e-05</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
@@ -6627,7 +6627,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="AG59" s="165" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="AH59" s="166" t="n">
         <v>0</v>
@@ -6745,13 +6745,13 @@
         <v>0.008428433635646842</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.007843858906676762</v>
+        <v>0.00784385890667676</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.007294725518855326</v>
       </c>
       <c r="F61" s="162" t="n">
-        <v>0.0002656841428881554</v>
+        <v>0.0002656841428881552</v>
       </c>
       <c r="G61" s="163" t="n">
         <v>0</v>
@@ -6763,10 +6763,10 @@
         <v>0.0006857327976666437</v>
       </c>
       <c r="J61" s="162" t="n">
-        <v>0.0006709355935762727</v>
+        <v>0.0006709355935762726</v>
       </c>
       <c r="K61" s="162" t="n">
-        <v>2.604903878032917e-05</v>
+        <v>2.604903878032915e-05</v>
       </c>
       <c r="L61" s="163" t="n">
         <v>0</v>
@@ -6781,7 +6781,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="P61" s="165" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="Q61" s="166" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
         <v>0.007488654907095417</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002727178664717763</v>
+        <v>0.0002727178664717761</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
@@ -6813,10 +6813,10 @@
         <v>0.0008028226133383132</v>
       </c>
       <c r="AA61" s="162" t="n">
-        <v>0.0007850633437809194</v>
+        <v>0.0007850633437809195</v>
       </c>
       <c r="AB61" s="162" t="n">
-        <v>3.045641678851837e-05</v>
+        <v>3.045641678851834e-05</v>
       </c>
       <c r="AC61" s="163" t="n">
         <v>0</v>
@@ -6831,7 +6831,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="AG61" s="165" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="AH61" s="166" t="n">
         <v>0</v>
@@ -6949,13 +6949,13 @@
         <v>0.007192523725370248</v>
       </c>
       <c r="D63" s="180" t="n">
-        <v>0.006659219699978683</v>
+        <v>0.006659219699978682</v>
       </c>
       <c r="E63" s="180" t="n">
-        <v>0.006155974440520869</v>
+        <v>0.00615597444052087</v>
       </c>
       <c r="F63" s="180" t="n">
-        <v>0.0002231900687600516</v>
+        <v>0.0002231900687600515</v>
       </c>
       <c r="G63" s="181" t="n">
         <v>0</v>
@@ -6967,10 +6967,10 @@
         <v>0.0006739117187029044</v>
       </c>
       <c r="J63" s="180" t="n">
-        <v>0.0006583058111807134</v>
+        <v>0.0006583058111807135</v>
       </c>
       <c r="K63" s="180" t="n">
-        <v>2.551168368675323e-05</v>
+        <v>2.551168368675321e-05</v>
       </c>
       <c r="L63" s="181" t="n">
         <v>0</v>
@@ -6985,7 +6985,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="P63" s="183" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="Q63" s="184" t="n">
         <v>0</v>
@@ -7005,7 +7005,7 @@
         <v>0.00594076232869969</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002150522189293122</v>
+        <v>0.000215052218929312</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
@@ -7014,13 +7014,13 @@
         <v>0.0008005063699695606</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.0007807151324075066</v>
+        <v>0.0007807151324075065</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0.0007614921589678736</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>2.945614065463415e-05</v>
+        <v>2.945614065463413e-05</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7035,7 +7035,7 @@
         <v>1049.434497201276</v>
       </c>
       <c r="AG63" s="189" t="n">
-        <v>41.19370833603934</v>
+        <v>41.19370833603931</v>
       </c>
       <c r="AH63" s="190" t="n">
         <v>0</v>
@@ -7306,7 +7306,7 @@
         <v>0.008483086307659215</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.01035731027260418</v>
+        <v>0.01035731027260417</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.01206934436206961</v>
@@ -7321,13 +7321,13 @@
         <v>0.0008160733808628929</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.001062740523966821</v>
+        <v>0.00106274052396682</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.001334437204275769</v>
       </c>
       <c r="M68" s="151" t="n">
-        <v>453.7255813321974</v>
+        <v>453.7255813321975</v>
       </c>
       <c r="N68" s="152" t="n">
         <v>710.315668023823</v>
@@ -7336,7 +7336,7 @@
         <v>1005.175876485817</v>
       </c>
       <c r="P68" s="152" t="n">
-        <v>1325.422170010491</v>
+        <v>1325.42217001049</v>
       </c>
       <c r="Q68" s="153" t="n">
         <v>1690.341010342051</v>
@@ -7347,7 +7347,7 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.00447067303154537</v>
+        <v>0.004470673031545371</v>
       </c>
       <c r="U68" s="149" t="n">
         <v>0.006520453533702532</v>
@@ -7356,13 +7356,13 @@
         <v>0.008626234805094208</v>
       </c>
       <c r="W68" s="149" t="n">
-        <v>0.01053208550760947</v>
+        <v>0.01053208550760946</v>
       </c>
       <c r="X68" s="150" t="n">
         <v>0.01227300944901985</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.0004617666947080962</v>
+        <v>0.0004617666947080963</v>
       </c>
       <c r="Z68" s="149" t="n">
         <v>0.0007111228743822203</v>
@@ -7371,13 +7371,13 @@
         <v>0.0009916266084152698</v>
       </c>
       <c r="AB68" s="149" t="n">
-        <v>0.001289574215990147</v>
+        <v>0.001289574215990146</v>
       </c>
       <c r="AC68" s="150" t="n">
         <v>0.001616491969649255</v>
       </c>
       <c r="AD68" s="151" t="n">
-        <v>453.7255813321974</v>
+        <v>453.7255813321975</v>
       </c>
       <c r="AE68" s="152" t="n">
         <v>710.315668023823</v>
@@ -7386,7 +7386,7 @@
         <v>1005.175876485817</v>
       </c>
       <c r="AG68" s="152" t="n">
-        <v>1325.422170010491</v>
+        <v>1325.42217001049</v>
       </c>
       <c r="AH68" s="153" t="n">
         <v>1690.341010342051</v>
@@ -7501,7 +7501,7 @@
         </is>
       </c>
       <c r="C70" s="161" t="n">
-        <v>0.003764019137838295</v>
+        <v>0.003764019137838296</v>
       </c>
       <c r="D70" s="162" t="n">
         <v>0.005527594678058097</v>
@@ -7510,13 +7510,13 @@
         <v>0.00734087107834956</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.008976209188679201</v>
+        <v>0.008976209188679196</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.01047182351423702</v>
       </c>
       <c r="H70" s="161" t="n">
-        <v>0.000310396955745724</v>
+        <v>0.0003103969557457241</v>
       </c>
       <c r="I70" s="162" t="n">
         <v>0.0004793575152121667</v>
@@ -7525,13 +7525,13 @@
         <v>0.0006701887346265468</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.0008740561736083294</v>
+        <v>0.0008740561736083289</v>
       </c>
       <c r="L70" s="163" t="n">
-        <v>0.001099308670174252</v>
+        <v>0.001099308670174245</v>
       </c>
       <c r="M70" s="164" t="n">
-        <v>453.7255813321974</v>
+        <v>453.7255813321975</v>
       </c>
       <c r="N70" s="165" t="n">
         <v>710.315668023823</v>
@@ -7540,7 +7540,7 @@
         <v>1005.175876485817</v>
       </c>
       <c r="P70" s="165" t="n">
-        <v>1325.422170010491</v>
+        <v>1325.42217001049</v>
       </c>
       <c r="Q70" s="166" t="n">
         <v>1690.341010342051</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003826911084328952</v>
+        <v>0.003826911084328953</v>
       </c>
       <c r="U70" s="162" t="n">
         <v>0.005619991271029435</v>
@@ -7560,7 +7560,7 @@
         <v>0.007463605590440982</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.009126298931424534</v>
+        <v>0.009126298931424527</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01064693305685051</v>
@@ -7575,13 +7575,13 @@
         <v>0.0007849030493053499</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.001022808723463227</v>
+        <v>0.001022808723463226</v>
       </c>
       <c r="AC70" s="163" t="n">
-        <v>0.001285011692131871</v>
+        <v>0.001285011692131862</v>
       </c>
       <c r="AD70" s="164" t="n">
-        <v>453.7255813321974</v>
+        <v>453.7255813321975</v>
       </c>
       <c r="AE70" s="165" t="n">
         <v>710.315668023823</v>
@@ -7590,7 +7590,7 @@
         <v>1005.175876485817</v>
       </c>
       <c r="AG70" s="165" t="n">
-        <v>1325.422170010491</v>
+        <v>1325.42217001049</v>
       </c>
       <c r="AH70" s="166" t="n">
         <v>1690.341010342051</v>
@@ -7606,7 +7606,7 @@
         <v>0.01198272553188943</v>
       </c>
       <c r="D71" s="156" t="n">
-        <v>0.01787647302587098</v>
+        <v>0.01787647302587099</v>
       </c>
       <c r="E71" s="156" t="n">
         <v>0.02409967911131486</v>
@@ -7615,13 +7615,13 @@
         <v>0.02996632524770066</v>
       </c>
       <c r="G71" s="157" t="n">
-        <v>0.03564412007955491</v>
+        <v>0.03564412007955492</v>
       </c>
       <c r="H71" s="155" t="n">
         <v>0.001200161236167245</v>
       </c>
       <c r="I71" s="156" t="n">
-        <v>0.001855379520059782</v>
+        <v>0.001855379520059783</v>
       </c>
       <c r="J71" s="156" t="n">
         <v>0.002598806725018306</v>
@@ -7630,13 +7630,13 @@
         <v>0.003406808126889305</v>
       </c>
       <c r="L71" s="157" t="n">
-        <v>0.004293971853995305</v>
+        <v>0.004293971853995306</v>
       </c>
       <c r="M71" s="158" t="n">
         <v>75.35870515216855</v>
       </c>
       <c r="N71" s="159" t="n">
-        <v>117.9407516252103</v>
+        <v>117.9407516252104</v>
       </c>
       <c r="O71" s="159" t="n">
         <v>167.0927875550783</v>
@@ -7645,7 +7645,7 @@
         <v>221.3977251165526</v>
       </c>
       <c r="Q71" s="160" t="n">
-        <v>282.7994204456232</v>
+        <v>282.7994204456233</v>
       </c>
       <c r="S71" s="32" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>0.01521742936613053</v>
       </c>
       <c r="U71" s="156" t="n">
-        <v>0.02270217780276865</v>
+        <v>0.02270217780276866</v>
       </c>
       <c r="V71" s="156" t="n">
         <v>0.03060532127243164</v>
@@ -7665,13 +7665,13 @@
         <v>0.03805565241445327</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.04526615236116274</v>
+        <v>0.04526615236116276</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.00137399115938798</v>
       </c>
       <c r="Z71" s="156" t="n">
-        <v>0.002124955260778551</v>
+        <v>0.002124955260778552</v>
       </c>
       <c r="AA71" s="156" t="n">
         <v>0.002977717864607578</v>
@@ -7680,13 +7680,13 @@
         <v>0.003906032132928865</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.004926860824961242</v>
+        <v>0.004926860824961244</v>
       </c>
       <c r="AD71" s="158" t="n">
         <v>75.35870515216855</v>
       </c>
       <c r="AE71" s="159" t="n">
-        <v>117.9407516252103</v>
+        <v>117.9407516252104</v>
       </c>
       <c r="AF71" s="159" t="n">
         <v>167.0927875550783</v>
@@ -7695,7 +7695,7 @@
         <v>221.3977251165526</v>
       </c>
       <c r="AH71" s="160" t="n">
-        <v>282.7994204456232</v>
+        <v>282.7994204456233</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" thickTop="1">
@@ -7705,49 +7705,49 @@
         </is>
       </c>
       <c r="C72" s="161" t="n">
-        <v>0.004171543103438437</v>
+        <v>0.004171543103438438</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.006130640949447838</v>
+        <v>0.006130640949447837</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.00814855825812771</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.009976414715730545</v>
+        <v>0.00997641471573054</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.01165112039890256</v>
       </c>
       <c r="H72" s="161" t="n">
-        <v>0.0003470430116006388</v>
+        <v>0.0003470430116006389</v>
       </c>
       <c r="I72" s="162" t="n">
         <v>0.0005359583362949184</v>
       </c>
       <c r="J72" s="162" t="n">
-        <v>0.0007494672359605999</v>
+        <v>0.0007494672359605998</v>
       </c>
       <c r="K72" s="162" t="n">
-        <v>0.0009781389698071336</v>
+        <v>0.000978138969807133</v>
       </c>
       <c r="L72" s="163" t="n">
-        <v>0.001230521265724046</v>
+        <v>0.001230521265724038</v>
       </c>
       <c r="M72" s="164" t="n">
-        <v>529.084286484366</v>
+        <v>529.0842864843661</v>
       </c>
       <c r="N72" s="165" t="n">
-        <v>828.2564196490333</v>
+        <v>828.2564196490334</v>
       </c>
       <c r="O72" s="165" t="n">
         <v>1172.268664040895</v>
       </c>
       <c r="P72" s="165" t="n">
-        <v>1546.819895127044</v>
+        <v>1546.819895127043</v>
       </c>
       <c r="Q72" s="166" t="n">
-        <v>1973.140430787674</v>
+        <v>1973.140430787675</v>
       </c>
       <c r="S72" s="42" t="inlineStr">
         <is>
@@ -7755,10 +7755,10 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004283599051273746</v>
+        <v>0.004283599051273747</v>
       </c>
       <c r="U72" s="162" t="n">
-        <v>0.006294410740017703</v>
+        <v>0.006294410740017704</v>
       </c>
       <c r="V72" s="162" t="n">
         <v>0.008365186685606284</v>
@@ -7767,37 +7767,37 @@
         <v>0.01024053037842388</v>
       </c>
       <c r="X72" s="163" t="n">
-        <v>0.01195765383894682</v>
+        <v>0.01195765383894681</v>
       </c>
       <c r="Y72" s="161" t="n">
         <v>0.0004065053023700545</v>
       </c>
       <c r="Z72" s="162" t="n">
-        <v>0.0006274739572744095</v>
+        <v>0.0006274739572744096</v>
       </c>
       <c r="AA72" s="162" t="n">
-        <v>0.0008769534064830982</v>
+        <v>0.0008769534064830984</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.001143635601787898</v>
+        <v>0.001143635601787897</v>
       </c>
       <c r="AC72" s="163" t="n">
-        <v>0.001437281583011477</v>
+        <v>0.001437281583011467</v>
       </c>
       <c r="AD72" s="164" t="n">
-        <v>529.084286484366</v>
+        <v>529.0842864843661</v>
       </c>
       <c r="AE72" s="165" t="n">
-        <v>828.2564196490333</v>
+        <v>828.2564196490334</v>
       </c>
       <c r="AF72" s="165" t="n">
         <v>1172.268664040895</v>
       </c>
       <c r="AG72" s="165" t="n">
-        <v>1546.819895127044</v>
+        <v>1546.819895127043</v>
       </c>
       <c r="AH72" s="166" t="n">
-        <v>1973.140430787674</v>
+        <v>1973.140430787675</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" thickBot="1">
@@ -7909,7 +7909,7 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.00355984564154226</v>
+        <v>0.003559845641542261</v>
       </c>
       <c r="D74" s="180" t="n">
         <v>0.005204744943755709</v>
@@ -7918,7 +7918,7 @@
         <v>0.006876518689355814</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.008380766206736076</v>
+        <v>0.008380766206736071</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.009747469824794498</v>
@@ -7927,31 +7927,31 @@
         <v>0.0003415426292077326</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.0005267191605749078</v>
+        <v>0.0005267191605749079</v>
       </c>
       <c r="J74" s="180" t="n">
-        <v>0.0007353591633029408</v>
+        <v>0.0007353591633029409</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.0009579613363027489</v>
+        <v>0.0009579613363027484</v>
       </c>
       <c r="L74" s="181" t="n">
-        <v>0.001202682673070541</v>
+        <v>0.001202682673070534</v>
       </c>
       <c r="M74" s="182" t="n">
-        <v>529.084286484366</v>
+        <v>529.0842864843661</v>
       </c>
       <c r="N74" s="183" t="n">
-        <v>828.2564196490333</v>
+        <v>828.2564196490334</v>
       </c>
       <c r="O74" s="183" t="n">
         <v>1172.268664040895</v>
       </c>
       <c r="P74" s="183" t="n">
-        <v>1546.819895127044</v>
+        <v>1546.819895127043</v>
       </c>
       <c r="Q74" s="184" t="n">
-        <v>1973.140430787674</v>
+        <v>1973.140430787675</v>
       </c>
       <c r="S74" s="51" t="inlineStr">
         <is>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003448683248069131</v>
+        <v>0.003448683248069132</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.005033106489159099</v>
@@ -7968,7 +7968,7 @@
         <v>0.006636116438922031</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008075190706733534</v>
+        <v>0.008075190706733529</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.009378492822202445</v>
@@ -7983,25 +7983,25 @@
         <v>0.0008506232625776511</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.001106075326517434</v>
+        <v>0.001106075326517433</v>
       </c>
       <c r="AC74" s="187" t="n">
-        <v>0.001385635093221026</v>
+        <v>0.001385635093221017</v>
       </c>
       <c r="AD74" s="188" t="n">
-        <v>529.084286484366</v>
+        <v>529.0842864843661</v>
       </c>
       <c r="AE74" s="189" t="n">
-        <v>828.2564196490333</v>
+        <v>828.2564196490334</v>
       </c>
       <c r="AF74" s="189" t="n">
         <v>1172.268664040895</v>
       </c>
       <c r="AG74" s="189" t="n">
-        <v>1546.819895127044</v>
+        <v>1546.819895127043</v>
       </c>
       <c r="AH74" s="190" t="n">
-        <v>1973.140430787674</v>
+        <v>1973.140430787675</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" thickBot="1"/>
@@ -8269,7 +8269,7 @@
         <v>558.4403689618165</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>600.5499545928172</v>
+        <v>600.5499545928175</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>642.4350718778161</v>
@@ -8284,7 +8284,7 @@
         <v>53.72199496514878</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>61.6210924085553</v>
+        <v>61.62109240855531</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>71.03030914749129</v>
@@ -8299,7 +8299,7 @@
         <v>66170585.44240464</v>
       </c>
       <c r="P79" s="152" t="n">
-        <v>76852213.85339233</v>
+        <v>76852213.85339235</v>
       </c>
       <c r="Q79" s="153" t="n">
         <v>89974593.14276318</v>
@@ -8319,7 +8319,7 @@
         <v>567.8638142533905</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>610.6839813510969</v>
+        <v>610.683981351097</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>653.275892294298</v>
@@ -8334,7 +8334,7 @@
         <v>65.27863904623896</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>74.77363489876672</v>
+        <v>74.77363489876673</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>86.04370739269012</v>
@@ -8349,7 +8349,7 @@
         <v>66170585.44240464</v>
       </c>
       <c r="AG79" s="152" t="n">
-        <v>76852213.85339233</v>
+        <v>76852213.85339235</v>
       </c>
       <c r="AH79" s="153" t="n">
         <v>89974593.14276318</v>
@@ -8362,7 +8362,7 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>906.4047888497506</v>
+        <v>906.4047888497505</v>
       </c>
       <c r="D80" s="156" t="n">
         <v>1030.020376359246</v>
@@ -8377,19 +8377,19 @@
         <v>1293.006067454048</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>59.26101965818171</v>
+        <v>59.2610196581817</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>68.45765238623693</v>
+        <v>68.4576523862369</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>78.453128616621</v>
+        <v>78.45312861662099</v>
       </c>
       <c r="K80" s="156" t="n">
         <v>89.13737808616851</v>
       </c>
       <c r="L80" s="157" t="n">
-        <v>101.9655727093285</v>
+        <v>101.965572709325</v>
       </c>
       <c r="M80" s="158" t="n">
         <v>15717905.29718792</v>
@@ -8404,7 +8404,7 @@
         <v>23998460.41759009</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>27625836.20539866</v>
+        <v>27625836.20539874</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>920.6559837956144</v>
+        <v>920.6559837956142</v>
       </c>
       <c r="U80" s="156" t="n">
         <v>1046.215150881935</v>
@@ -8424,22 +8424,22 @@
         <v>1237.994812550095</v>
       </c>
       <c r="X80" s="157" t="n">
-        <v>1313.335705779168</v>
+        <v>1313.335705779169</v>
       </c>
       <c r="Y80" s="155" t="n">
         <v>59.51258517114454</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>68.74915746681961</v>
+        <v>68.74915746681958</v>
       </c>
       <c r="AA80" s="156" t="n">
-        <v>78.78938908278754</v>
+        <v>78.78938908278752</v>
       </c>
       <c r="AB80" s="156" t="n">
         <v>89.52416199621217</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>102.4151112868439</v>
+        <v>102.4151112868404</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>15717905.29718792</v>
@@ -8454,7 +8454,7 @@
         <v>23998460.41759009</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>27625836.20539866</v>
+        <v>27625836.20539874</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8467,16 +8467,16 @@
         <v>520.9253145439409</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>581.4346859436331</v>
+        <v>581.434685943633</v>
       </c>
       <c r="E81" s="162" t="n">
         <v>636.8661517998537</v>
       </c>
       <c r="F81" s="162" t="n">
-        <v>682.9950257045424</v>
+        <v>682.9950257045425</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>728.5458577871523</v>
+        <v>728.5458577871524</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>42.95770714337677</v>
@@ -8488,16 +8488,16 @@
         <v>58.14303450445336</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>66.50647352489749</v>
+        <v>66.5064735248975</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>76.48111878471697</v>
+        <v>76.48111878471651</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>62793820.25348816</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>74716434.79897219</v>
+        <v>74716434.79897217</v>
       </c>
       <c r="O81" s="165" t="n">
         <v>87205249.28269063</v>
@@ -8506,7 +8506,7 @@
         <v>100850674.2709824</v>
       </c>
       <c r="Q81" s="166" t="n">
-        <v>117600429.3481618</v>
+        <v>117600429.3481619</v>
       </c>
       <c r="S81" s="42" t="inlineStr">
         <is>
@@ -8517,22 +8517,22 @@
         <v>529.6293104079848</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>591.1536662859879</v>
+        <v>591.1536662859878</v>
       </c>
       <c r="V81" s="162" t="n">
         <v>647.5141328874428</v>
       </c>
       <c r="W81" s="162" t="n">
-        <v>694.4152751160225</v>
+        <v>694.4152751160226</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>740.7285814318559</v>
+        <v>740.728581431856</v>
       </c>
       <c r="Y81" s="161" t="n">
         <v>50.36815663552992</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>59.08854170698643</v>
+        <v>59.08854170698641</v>
       </c>
       <c r="AA81" s="162" t="n">
         <v>68.09521366222606</v>
@@ -8541,13 +8541,13 @@
         <v>77.82497663419404</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>89.40085212837401</v>
+        <v>89.4008521283734</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>62793820.25348816</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>74716434.79897219</v>
+        <v>74716434.79897217</v>
       </c>
       <c r="AF81" s="165" t="n">
         <v>87205249.28269063</v>
@@ -8556,7 +8556,7 @@
         <v>100850674.2709824</v>
       </c>
       <c r="AH81" s="166" t="n">
-        <v>117600429.3481618</v>
+        <v>117600429.3481619</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" thickBot="1">
@@ -8575,7 +8575,7 @@
         <v>1124.867408518502</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>1216.101966930558</v>
+        <v>1216.101966930559</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>1311.604254483836</v>
@@ -8587,7 +8587,7 @@
         <v>106.4608024544716</v>
       </c>
       <c r="J82" s="156" t="n">
-        <v>121.300909132823</v>
+        <v>121.3009091328231</v>
       </c>
       <c r="K82" s="156" t="n">
         <v>138.2560600880815</v>
@@ -8602,10 +8602,10 @@
         <v>6767384.744927467</v>
       </c>
       <c r="O82" s="159" t="n">
-        <v>7799159.069755712</v>
+        <v>7799159.069755713</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>8984825.692261012</v>
+        <v>8984825.692261014</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>10406230.31776842</v>
@@ -8622,7 +8622,7 @@
         <v>1302.64026320015</v>
       </c>
       <c r="V82" s="156" t="n">
-        <v>1428.522274822855</v>
+        <v>1428.522274822856</v>
       </c>
       <c r="W82" s="156" t="n">
         <v>1544.385351607079</v>
@@ -8652,10 +8652,10 @@
         <v>6767384.744927467</v>
       </c>
       <c r="AF82" s="159" t="n">
-        <v>7799159.069755712</v>
+        <v>7799159.069755713</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>8984825.692261012</v>
+        <v>8984825.692261014</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>10406230.31776842</v>
@@ -8671,37 +8671,37 @@
         <v>540.5578862727502</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>603.1321085623804</v>
+        <v>603.1321085623802</v>
       </c>
       <c r="E83" s="162" t="n">
         <v>660.3852683141049</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>708.3982444206447</v>
+        <v>708.3982444206449</v>
       </c>
       <c r="G83" s="163" t="n">
-        <v>755.8615597541253</v>
+        <v>755.8615597541254</v>
       </c>
       <c r="H83" s="161" t="n">
         <v>44.97060971081473</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>52.72755069765644</v>
+        <v>52.72755069765643</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>60.73922601201267</v>
+        <v>60.73922601201266</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>69.45500450359449</v>
+        <v>69.45500450359451</v>
       </c>
       <c r="L83" s="163" t="n">
-        <v>79.82955212688435</v>
+        <v>79.8295521268839</v>
       </c>
       <c r="M83" s="164" t="n">
         <v>68559925.30111365</v>
       </c>
       <c r="N83" s="165" t="n">
-        <v>81483819.54389966</v>
+        <v>81483819.54389964</v>
       </c>
       <c r="O83" s="165" t="n">
         <v>95004408.35244635</v>
@@ -8721,37 +8721,37 @@
         <v>555.0783466405735</v>
       </c>
       <c r="U83" s="162" t="n">
-        <v>619.243771261224</v>
+        <v>619.2437712612239</v>
       </c>
       <c r="V83" s="162" t="n">
         <v>677.9415301303848</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>727.1523837690163</v>
+        <v>727.1523837690164</v>
       </c>
       <c r="X83" s="163" t="n">
-        <v>775.7477883893105</v>
+        <v>775.7477883893106</v>
       </c>
       <c r="Y83" s="161" t="n">
         <v>52.67586635427527</v>
       </c>
       <c r="Z83" s="162" t="n">
-        <v>61.73085229416038</v>
+        <v>61.73085229416036</v>
       </c>
       <c r="AA83" s="162" t="n">
-        <v>71.07111372268385</v>
+        <v>71.07111372268386</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>81.20647303144611</v>
+        <v>81.20647303144609</v>
       </c>
       <c r="AC83" s="163" t="n">
-        <v>93.24304117939265</v>
+        <v>93.24304117939202</v>
       </c>
       <c r="AD83" s="164" t="n">
         <v>68559925.30111365</v>
       </c>
       <c r="AE83" s="165" t="n">
-        <v>81483819.54389966</v>
+        <v>81483819.54389964</v>
       </c>
       <c r="AF83" s="165" t="n">
         <v>95004408.35244635</v>
@@ -8770,7 +8770,7 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>3077.561852826308</v>
+        <v>3077.561852826309</v>
       </c>
       <c r="D84" s="156" t="n">
         <v>3276.191295399594</v>
@@ -8782,7 +8782,7 @@
         <v>3722.77992925921</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>3974.81460749317</v>
+        <v>3974.814607493171</v>
       </c>
       <c r="H84" s="155" t="n">
         <v>2731.81260038769</v>
@@ -8797,10 +8797,10 @@
         <v>3299.321888233776</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>3541.909197954797</v>
+        <v>3541.909197954798</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>67071872.29194545</v>
+        <v>67071872.29194546</v>
       </c>
       <c r="N84" s="159" t="n">
         <v>78739189.42363153</v>
@@ -8812,7 +8812,7 @@
         <v>109897072.6029604</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>131462690.8423988</v>
+        <v>131462690.8423989</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8850,7 +8850,7 @@
         <v>2569.179492848509</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>67071872.29194545</v>
+        <v>67071872.29194546</v>
       </c>
       <c r="AE84" s="159" t="n">
         <v>78739189.42363153</v>
@@ -8862,7 +8862,7 @@
         <v>109897072.6029604</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>131462690.8423988</v>
+        <v>131462690.8423989</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>912.5734327217835</v>
+        <v>912.5734327217838</v>
       </c>
       <c r="D85" s="180" t="n">
         <v>1006.837829461618</v>
@@ -8884,22 +8884,22 @@
         <v>1190.524717508094</v>
       </c>
       <c r="G85" s="181" t="n">
-        <v>1281.799118337119</v>
+        <v>1281.79911833712</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>87.55512484015769</v>
+        <v>87.5551248401577</v>
       </c>
       <c r="I85" s="180" t="n">
         <v>101.891789530499</v>
       </c>
       <c r="J85" s="180" t="n">
-        <v>118.1017799659394</v>
+        <v>118.1017799659395</v>
       </c>
       <c r="K85" s="180" t="n">
         <v>136.0826231340094</v>
       </c>
       <c r="L85" s="181" t="n">
-        <v>158.1536150088723</v>
+        <v>158.1536150088715</v>
       </c>
       <c r="M85" s="182" t="n">
         <v>135631797.5930591</v>
@@ -8914,7 +8914,7 @@
         <v>219732572.5662038</v>
       </c>
       <c r="Q85" s="184" t="n">
-        <v>259469350.5083291</v>
+        <v>259469350.5083292</v>
       </c>
       <c r="S85" s="51" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>884.0767344892743</v>
+        <v>884.0767344892745</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>973.6350326011249</v>
@@ -8934,7 +8934,7 @@
         <v>1147.116373110476</v>
       </c>
       <c r="X85" s="187" t="n">
-        <v>1233.278383714672</v>
+        <v>1233.278383714673</v>
       </c>
       <c r="Y85" s="185" t="n">
         <v>101.5666925618895</v>
@@ -8946,10 +8946,10 @@
         <v>136.6136799596382</v>
       </c>
       <c r="AB85" s="186" t="n">
-        <v>157.1228671892135</v>
+        <v>157.1228671892134</v>
       </c>
       <c r="AC85" s="187" t="n">
-        <v>182.2119865721286</v>
+        <v>182.2119865721275</v>
       </c>
       <c r="AD85" s="188" t="n">
         <v>135631797.5930591</v>
@@ -8964,7 +8964,7 @@
         <v>219732572.5662038</v>
       </c>
       <c r="AH85" s="190" t="n">
-        <v>259469350.5083291</v>
+        <v>259469350.5083292</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" thickBot="1"/>
@@ -9416,7 +9416,7 @@
         <v>19689.72928516593</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>21365.5889951038</v>
+        <v>21365.58899510386</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>247890.8390778529</v>
@@ -9431,7 +9431,7 @@
         <v>249540.3168845894</v>
       </c>
       <c r="L91" s="81" t="n">
-        <v>249567.388394737</v>
+        <v>249567.388394747</v>
       </c>
       <c r="M91" s="79" t="n">
         <v>265231.7727209047</v>
@@ -9446,7 +9446,7 @@
         <v>269230.0461697553</v>
       </c>
       <c r="Q91" s="81" t="n">
-        <v>270932.9773898408</v>
+        <v>270932.9773898508</v>
       </c>
       <c r="S91" s="32" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>19384.9442455713</v>
       </c>
       <c r="X91" s="81" t="n">
-        <v>21034.86266598452</v>
+        <v>21034.86266598458</v>
       </c>
       <c r="Y91" s="79" t="n">
         <v>247038.1055676015</v>
@@ -9481,7 +9481,7 @@
         <v>248681.9092437189</v>
       </c>
       <c r="AC91" s="81" t="n">
-        <v>248708.8876290703</v>
+        <v>248708.8876290802</v>
       </c>
       <c r="AD91" s="79" t="n">
         <v>264110.6120997236</v>
@@ -9496,7 +9496,7 @@
         <v>268066.8534892902</v>
       </c>
       <c r="AH91" s="81" t="n">
-        <v>269743.7502950548</v>
+        <v>269743.7502950648</v>
       </c>
       <c r="AJ91" s="120" t="n">
         <v>88.60685471261492</v>
@@ -9551,7 +9551,7 @@
         <v>1368744.420106977</v>
       </c>
       <c r="L92" s="87" t="n">
-        <v>1376222.004999609</v>
+        <v>1376222.004999619</v>
       </c>
       <c r="M92" s="85" t="n">
         <v>1461759.121451847</v>
@@ -9566,7 +9566,7 @@
         <v>1516403.876582447</v>
       </c>
       <c r="Q92" s="87" t="n">
-        <v>1537640.024320116</v>
+        <v>1537640.024320126</v>
       </c>
       <c r="S92" s="42" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>145231.0712118658</v>
       </c>
       <c r="X92" s="87" t="n">
-        <v>158763.1857283485</v>
+        <v>158763.1857283486</v>
       </c>
       <c r="Y92" s="85" t="n">
         <v>1128134.981019596</v>
@@ -9601,7 +9601,7 @@
         <v>1150634.069166108</v>
       </c>
       <c r="AC92" s="87" t="n">
-        <v>1156665.320247132</v>
+        <v>1156665.320247141</v>
       </c>
       <c r="AD92" s="85" t="n">
         <v>1246696.811000487</v>
@@ -9616,7 +9616,7 @@
         <v>1295865.140377974</v>
       </c>
       <c r="AH92" s="87" t="n">
-        <v>1315428.50597548</v>
+        <v>1315428.50597549</v>
       </c>
       <c r="AJ92" s="126" t="n">
         <v>38.68723939856347</v>
@@ -9759,16 +9759,16 @@
         <v>126831.7918250114</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>135101.1136484238</v>
+        <v>135101.1136484239</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>143862.0952205411</v>
       </c>
       <c r="F94" s="86" t="n">
-        <v>155047.6738590327</v>
+        <v>155047.6738590326</v>
       </c>
       <c r="G94" s="87" t="n">
-        <v>169351.990472395</v>
+        <v>169351.9904723951</v>
       </c>
       <c r="H94" s="85" t="n">
         <v>1397717.813839464</v>
@@ -9783,7 +9783,7 @@
         <v>1426343.05166542</v>
       </c>
       <c r="L94" s="87" t="n">
-        <v>1434147.669183358</v>
+        <v>1434147.669183368</v>
       </c>
       <c r="M94" s="85" t="n">
         <v>1524549.605664476</v>
@@ -9798,7 +9798,7 @@
         <v>1581390.725524453</v>
       </c>
       <c r="Q94" s="87" t="n">
-        <v>1603499.659655753</v>
+        <v>1603499.659655763</v>
       </c>
       <c r="S94" s="42" t="inlineStr">
         <is>
@@ -9818,7 +9818,7 @@
         <v>151048.8068455996</v>
       </c>
       <c r="X94" s="87" t="n">
-        <v>165010.6665875403</v>
+        <v>165010.6665875404</v>
       </c>
       <c r="Y94" s="85" t="n">
         <v>1178029.421998275</v>
@@ -9830,10 +9830,10 @@
         <v>1196614.784709081</v>
       </c>
       <c r="AB94" s="86" t="n">
-        <v>1201497.312485443</v>
+        <v>1201497.312485444</v>
       </c>
       <c r="AC94" s="87" t="n">
-        <v>1207817.354107913</v>
+        <v>1207817.354107923</v>
       </c>
       <c r="AD94" s="85" t="n">
         <v>1301543.38307431</v>
@@ -9848,7 +9848,7 @@
         <v>1352546.119331043</v>
       </c>
       <c r="AH94" s="87" t="n">
-        <v>1372828.020695454</v>
+        <v>1372828.020695464</v>
       </c>
       <c r="AJ94" s="126" t="n">
         <v>40.55521070797514</v>
@@ -10015,7 +10015,7 @@
         <v>1430131.875877583</v>
       </c>
       <c r="L96" s="134" t="n">
-        <v>1438190.087282662</v>
+        <v>1438190.087282672</v>
       </c>
       <c r="M96" s="132" t="n">
         <v>1549101.755501704</v>
@@ -10030,7 +10030,7 @@
         <v>1614699.713348551</v>
       </c>
       <c r="Q96" s="134" t="n">
-        <v>1640615.995364842</v>
+        <v>1640615.995364852</v>
       </c>
       <c r="S96" s="51" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>1206923.968031044</v>
       </c>
       <c r="AC96" s="137" t="n">
-        <v>1213607.226999297</v>
+        <v>1213607.226999307</v>
       </c>
       <c r="AD96" s="135" t="n">
         <v>1335396.419553705</v>
@@ -10080,7 +10080,7 @@
         <v>1398476.087516869</v>
       </c>
       <c r="AH96" s="137" t="n">
-        <v>1423997.155124689</v>
+        <v>1423997.155124698</v>
       </c>
       <c r="AJ96" s="138" t="n"/>
       <c r="AK96" s="139" t="n"/>
